--- a/qmd/chapter_1/downloads/receiver_log_complete.xlsx
+++ b/qmd/chapter_1/downloads/receiver_log_complete.xlsx
@@ -621,7 +621,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SG-7F7ERPI3I522</t>
+          <t>SG-7F7ERPI31522</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SG-3315RPI33AD3</t>
+          <t>SG-E3E4RPI4CED5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SG-3315RPI33AD3</t>
+          <t>SG-E3E4RPI4CED5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SG-E3E4RPI4CE25</t>
+          <t>SG-E3E4RPI4CED5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
